--- a/students.xlsx
+++ b/students.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
         <v>56</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>형욱</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
